--- a/rates-nodispo/week-21/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-21/Analisis_Rates_NoDispo_7d.xlsx
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10142,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14745,7 +14745,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17813,7 +17813,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21406,7 +21406,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23594,7 +23594,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23747,7 +23747,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23900,7 +23900,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24061,7 +24061,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29169,7 +29169,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -33164,7 +33164,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -37767,7 +37767,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -41010,7 +41010,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -44603,7 +44603,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47771,7 +47771,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47924,7 +47924,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48085,7 +48085,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -53193,7 +53193,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -57190,7 +57190,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -59955,7 +59955,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -64558,7 +64558,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -67731,7 +67731,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -71324,7 +71324,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -75375,7 +75375,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -77982,7 +77982,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -79871,7 +79871,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -83656,7 +83656,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -87555,7 +87555,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -91451,7 +91451,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-21/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-21/Analisis_Rates_NoDispo_7d.xlsx
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10142,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14745,7 +14745,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17813,7 +17813,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21406,7 +21406,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23594,7 +23594,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23747,7 +23747,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23900,7 +23900,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24061,7 +24061,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29169,7 +29169,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -33164,7 +33164,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -37767,7 +37767,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -41010,7 +41010,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -44603,7 +44603,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47771,7 +47771,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47924,7 +47924,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48085,7 +48085,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -53193,7 +53193,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -57190,7 +57190,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -59955,7 +59955,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -64558,7 +64558,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -67731,7 +67731,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -71324,7 +71324,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -75375,7 +75375,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -77982,7 +77982,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -79871,7 +79871,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -83656,7 +83656,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -87555,7 +87555,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -91451,7 +91451,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-21/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-21/Analisis_Rates_NoDispo_7d.xlsx
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10142,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14745,7 +14745,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17813,7 +17813,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21406,7 +21406,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23594,7 +23594,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23747,7 +23747,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23900,7 +23900,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24061,7 +24061,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29169,7 +29169,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -33164,7 +33164,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -37767,7 +37767,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -41010,7 +41010,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -44603,7 +44603,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47771,7 +47771,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47924,7 +47924,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48085,7 +48085,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -53193,7 +53193,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -57190,7 +57190,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -59955,7 +59955,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -64558,7 +64558,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -67731,7 +67731,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -71324,7 +71324,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -75375,7 +75375,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -77982,7 +77982,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -79871,7 +79871,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -83656,7 +83656,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -87555,7 +87555,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -91451,7 +91451,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:10 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-21/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-21/Analisis_Rates_NoDispo_7d.xlsx
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10142,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14745,7 +14745,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17813,7 +17813,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21406,7 +21406,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23594,7 +23594,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23747,7 +23747,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23900,7 +23900,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24061,7 +24061,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29169,7 +29169,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -33164,7 +33164,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -37767,7 +37767,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -41010,7 +41010,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -44603,7 +44603,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47771,7 +47771,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47924,7 +47924,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48085,7 +48085,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -53193,7 +53193,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -57190,7 +57190,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -59955,7 +59955,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -64558,7 +64558,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -67731,7 +67731,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -71324,7 +71324,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -75375,7 +75375,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -77982,7 +77982,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -79871,7 +79871,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -83656,7 +83656,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -87555,7 +87555,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -91451,7 +91451,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-21/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-21/Analisis_Rates_NoDispo_7d.xlsx
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10142,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14745,7 +14745,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17813,7 +17813,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21406,7 +21406,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23594,7 +23594,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23747,7 +23747,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23900,7 +23900,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24061,7 +24061,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29169,7 +29169,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -33164,7 +33164,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -37767,7 +37767,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -41010,7 +41010,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -44603,7 +44603,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47771,7 +47771,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47924,7 +47924,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48085,7 +48085,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -53193,7 +53193,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -57190,7 +57190,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -59955,7 +59955,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -64558,7 +64558,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -67731,7 +67731,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -71324,7 +71324,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -75375,7 +75375,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -77982,7 +77982,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -79871,7 +79871,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -83656,7 +83656,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -87555,7 +87555,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -91451,7 +91451,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:26 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 25/05/2026 22:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
